--- a/data/05_modelado/results/results_lineales_ext.xlsx
+++ b/data/05_modelado/results/results_lineales_ext.xlsx
@@ -563,7 +563,7 @@
         <v>0.8373736705665914</v>
       </c>
       <c r="K2" t="n">
-        <v>4.623</v>
+        <v>1.206</v>
       </c>
       <c r="L2" t="n">
         <v>6.64</v>
@@ -628,7 +628,7 @@
         <v>0.8369655157638372</v>
       </c>
       <c r="K3" t="n">
-        <v>0.764</v>
+        <v>0.439</v>
       </c>
       <c r="L3" t="n">
         <v>6.64</v>
@@ -693,10 +693,10 @@
         <v>0.8552946160581802</v>
       </c>
       <c r="K4" t="n">
-        <v>0.822</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
-        <v>6.64</v>
+        <v>6.78</v>
       </c>
       <c r="M4" t="n">
         <v>0.7494</v>
@@ -758,7 +758,7 @@
         <v>0.821571559783296</v>
       </c>
       <c r="K5" t="n">
-        <v>3.093</v>
+        <v>1.413</v>
       </c>
       <c r="L5" t="n">
         <v>6.64</v>
@@ -823,7 +823,7 @@
         <v>0.8509814845146796</v>
       </c>
       <c r="K6" t="n">
-        <v>18.532</v>
+        <v>2.677</v>
       </c>
       <c r="L6" t="n">
         <v>6.64</v>
@@ -888,7 +888,7 @@
         <v>0.8190070569079394</v>
       </c>
       <c r="K7" t="n">
-        <v>2.54</v>
+        <v>2.077</v>
       </c>
       <c r="L7" t="n">
         <v>6.64</v>
@@ -953,7 +953,7 @@
         <v>0.8160317315513794</v>
       </c>
       <c r="K8" t="n">
-        <v>8.765000000000001</v>
+        <v>3.442</v>
       </c>
       <c r="L8" t="n">
         <v>6.64</v>
@@ -1018,7 +1018,7 @@
         <v>0.8214975628062042</v>
       </c>
       <c r="K9" t="n">
-        <v>8.106</v>
+        <v>2.642</v>
       </c>
       <c r="L9" t="n">
         <v>6.64</v>
@@ -1083,7 +1083,7 @@
         <v>0.8206423576195739</v>
       </c>
       <c r="K10" t="n">
-        <v>5.042</v>
+        <v>2.771</v>
       </c>
       <c r="L10" t="n">
         <v>6.9</v>
